--- a/artfynd/A 35797-2025 artfynd.xlsx
+++ b/artfynd/A 35797-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127499968</v>
       </c>
       <c r="B2" t="n">
-        <v>105478</v>
+        <v>105484</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127499994</v>
       </c>
       <c r="B3" t="n">
-        <v>92612</v>
+        <v>92616</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>127499983</v>
       </c>
       <c r="B4" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35797-2025 artfynd.xlsx
+++ b/artfynd/A 35797-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127499968</v>
+        <v>127499994</v>
       </c>
       <c r="B2" t="n">
-        <v>105484</v>
+        <v>92616</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,27 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>4363</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -714,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515669</v>
+        <v>515630</v>
       </c>
       <c r="R2" t="n">
-        <v>6522797</v>
+        <v>6522834</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127499994</v>
+        <v>127499968</v>
       </c>
       <c r="B3" t="n">
-        <v>92616</v>
+        <v>105484</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,26 +787,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4363</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515630</v>
+        <v>515669</v>
       </c>
       <c r="R3" t="n">
-        <v>6522834</v>
+        <v>6522797</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 35797-2025 artfynd.xlsx
+++ b/artfynd/A 35797-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>127499968</v>
       </c>
       <c r="B3" t="n">
-        <v>105484</v>
+        <v>105486</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35797-2025 artfynd.xlsx
+++ b/artfynd/A 35797-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127499994</v>
+        <v>127499968</v>
       </c>
       <c r="B2" t="n">
-        <v>92616</v>
+        <v>105488</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,26 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4363</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515630</v>
+        <v>515669</v>
       </c>
       <c r="R2" t="n">
-        <v>6522834</v>
+        <v>6522797</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127499968</v>
+        <v>127499994</v>
       </c>
       <c r="B3" t="n">
-        <v>105486</v>
+        <v>92618</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,27 +788,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>4363</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515669</v>
+        <v>515630</v>
       </c>
       <c r="R3" t="n">
-        <v>6522797</v>
+        <v>6522834</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +881,7 @@
         <v>127499983</v>
       </c>
       <c r="B4" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35797-2025 artfynd.xlsx
+++ b/artfynd/A 35797-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127499968</v>
+        <v>127499994</v>
       </c>
       <c r="B2" t="n">
-        <v>105488</v>
+        <v>92618</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,27 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>4363</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -714,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515669</v>
+        <v>515630</v>
       </c>
       <c r="R2" t="n">
-        <v>6522797</v>
+        <v>6522834</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127499994</v>
+        <v>127499968</v>
       </c>
       <c r="B3" t="n">
-        <v>92618</v>
+        <v>105488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,26 +787,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4363</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515630</v>
+        <v>515669</v>
       </c>
       <c r="R3" t="n">
-        <v>6522834</v>
+        <v>6522797</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 35797-2025 artfynd.xlsx
+++ b/artfynd/A 35797-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127499994</v>
       </c>
       <c r="B2" t="n">
-        <v>92618</v>
+        <v>92624</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127499968</v>
       </c>
       <c r="B3" t="n">
-        <v>105488</v>
+        <v>105494</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35797-2025 artfynd.xlsx
+++ b/artfynd/A 35797-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127499994</v>
       </c>
       <c r="B2" t="n">
-        <v>92624</v>
+        <v>92627</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127499968</v>
       </c>
       <c r="B3" t="n">
-        <v>105494</v>
+        <v>105497</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>127499983</v>
       </c>
       <c r="B4" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35797-2025 artfynd.xlsx
+++ b/artfynd/A 35797-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127499994</v>
       </c>
       <c r="B2" t="n">
-        <v>92627</v>
+        <v>92635</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127499968</v>
       </c>
       <c r="B3" t="n">
-        <v>105497</v>
+        <v>105505</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>127499983</v>
       </c>
       <c r="B4" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35797-2025 artfynd.xlsx
+++ b/artfynd/A 35797-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127499994</v>
+        <v>127499968</v>
       </c>
       <c r="B2" t="n">
-        <v>92635</v>
+        <v>105506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,26 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4363</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515630</v>
+        <v>515669</v>
       </c>
       <c r="R2" t="n">
-        <v>6522834</v>
+        <v>6522797</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127499968</v>
+        <v>127499994</v>
       </c>
       <c r="B3" t="n">
-        <v>105505</v>
+        <v>92636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,27 +788,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>4363</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515669</v>
+        <v>515630</v>
       </c>
       <c r="R3" t="n">
-        <v>6522797</v>
+        <v>6522834</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 35797-2025 artfynd.xlsx
+++ b/artfynd/A 35797-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127499968</v>
+        <v>127499994</v>
       </c>
       <c r="B2" t="n">
-        <v>105506</v>
+        <v>92636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,27 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>4363</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -714,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515669</v>
+        <v>515630</v>
       </c>
       <c r="R2" t="n">
-        <v>6522797</v>
+        <v>6522834</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127499994</v>
+        <v>127499968</v>
       </c>
       <c r="B3" t="n">
-        <v>92636</v>
+        <v>105506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,26 +787,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4363</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515630</v>
+        <v>515669</v>
       </c>
       <c r="R3" t="n">
-        <v>6522834</v>
+        <v>6522797</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 35797-2025 artfynd.xlsx
+++ b/artfynd/A 35797-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127499994</v>
       </c>
       <c r="B2" t="n">
-        <v>92636</v>
+        <v>92637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127499968</v>
       </c>
       <c r="B3" t="n">
-        <v>105506</v>
+        <v>105507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35797-2025 artfynd.xlsx
+++ b/artfynd/A 35797-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127499994</v>
       </c>
       <c r="B2" t="n">
-        <v>92637</v>
+        <v>92638</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127499968</v>
       </c>
       <c r="B3" t="n">
-        <v>105507</v>
+        <v>105508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35797-2025 artfynd.xlsx
+++ b/artfynd/A 35797-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127499994</v>
+        <v>127499968</v>
       </c>
       <c r="B2" t="n">
-        <v>92638</v>
+        <v>105508</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,26 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4363</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515630</v>
+        <v>515669</v>
       </c>
       <c r="R2" t="n">
-        <v>6522834</v>
+        <v>6522797</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127499968</v>
+        <v>127499994</v>
       </c>
       <c r="B3" t="n">
-        <v>105508</v>
+        <v>92638</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,27 +788,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>4363</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515669</v>
+        <v>515630</v>
       </c>
       <c r="R3" t="n">
-        <v>6522797</v>
+        <v>6522834</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
